--- a/EX1/CPa results/CPa_for_DeepJIT_test_data.xlsx
+++ b/EX1/CPa results/CPa_for_DeepJIT_test_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xhulj\Desktop\CPa\EX1\CP_res\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xhulj\Desktop\CPa\EX1\CPa results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15D15593-597F-4187-87CE-BEC0781A63EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C37BD27-41A2-47A0-A20A-BD29D8787F12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28220" yWindow="3470" windowWidth="24910" windowHeight="14110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="47385" yWindow="4485" windowWidth="19050" windowHeight="14115" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OP_0.05" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="75">
   <si>
     <t>Total correct made 
 by DeepJIT</t>
@@ -246,6 +246,24 @@
   </si>
   <si>
     <t>0,842863</t>
+  </si>
+  <si>
+    <t>Precision_clean</t>
+  </si>
+  <si>
+    <t>recall_clean</t>
+  </si>
+  <si>
+    <t>Precision faulty</t>
+  </si>
+  <si>
+    <t>recall_faulty</t>
+  </si>
+  <si>
+    <t>DeepJIT with Openstack makes 777 correct predictions; 639 clean and 138 fault-prone</t>
+  </si>
+  <si>
+    <t>DeepJIT with QT makes 1851 correct predictions; 1727 clean and 124 fault-prone</t>
   </si>
 </sst>
 </file>
@@ -256,7 +274,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -315,6 +333,19 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -366,7 +397,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -411,6 +442,13 @@
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -538,16 +576,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O97"/>
+  <dimension ref="A1:U97"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="2"/>
     <col min="2" max="6" width="12.6640625" style="1"/>
     <col min="7" max="7" width="24.21875" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="12.6640625" style="1"/>
+    <col min="8" max="16" width="12.6640625" style="1"/>
+    <col min="22" max="16384" width="12.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -591,8 +630,20 @@
       <c r="O1" s="5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q1" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>777</v>
       </c>
@@ -638,8 +689,24 @@
         <f t="shared" ref="O2:O9" si="1">G2/A2</f>
         <v>0.29214929214929214</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q2">
+        <f>J2/(J2+K2)</f>
+        <v>0.98989898989898994</v>
+      </c>
+      <c r="R2">
+        <f>J2/639</f>
+        <v>0.30672926447574334</v>
+      </c>
+      <c r="T2">
+        <f>I2/(I2+L2)</f>
+        <v>0.2767857142857143</v>
+      </c>
+      <c r="U2">
+        <f>I2/138</f>
+        <v>0.22463768115942029</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>777</v>
       </c>
@@ -685,8 +752,24 @@
         <f>G3/A3</f>
         <v>0.56885456885456886</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q3">
+        <f t="shared" ref="Q3:Q11" si="2">J3/(J3+K3)</f>
+        <v>0.98800959232613905</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R11" si="3">J3/639</f>
+        <v>0.64475743348982784</v>
+      </c>
+      <c r="T3">
+        <f t="shared" ref="T3:T11" si="4">I3/(I3+L3)</f>
+        <v>0.25862068965517243</v>
+      </c>
+      <c r="U3">
+        <f t="shared" ref="U3:U11" si="5">I3/138</f>
+        <v>0.21739130434782608</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>777</v>
       </c>
@@ -732,8 +815,24 @@
         <f t="shared" si="1"/>
         <v>0.30115830115830117</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q4">
+        <f t="shared" si="2"/>
+        <v>0.98598130841121501</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="3"/>
+        <v>0.33020344287949921</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="4"/>
+        <v>0.24731182795698925</v>
+      </c>
+      <c r="U4">
+        <f>I4/138</f>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>777</v>
       </c>
@@ -779,8 +878,24 @@
         <f t="shared" si="1"/>
         <v>0.56885456885456886</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q5">
+        <f t="shared" si="2"/>
+        <v>0.98337292161520184</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="3"/>
+        <v>0.647887323943662</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="5"/>
+        <v>0.20289855072463769</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>777</v>
       </c>
@@ -826,8 +941,24 @@
         <f t="shared" si="1"/>
         <v>0.4929214929214929</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q6">
+        <f t="shared" si="2"/>
+        <v>0.98360655737704916</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="3"/>
+        <v>0.56338028169014087</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="4"/>
+        <v>0.27380952380952384</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="5"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>777</v>
       </c>
@@ -873,8 +1004,24 @@
         <f t="shared" si="1"/>
         <v>0.38996138996138996</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q7">
+        <f t="shared" si="2"/>
+        <v>0.98233215547703179</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="3"/>
+        <v>0.4350547730829421</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="4"/>
+        <v>0.24038461538461539</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="5"/>
+        <v>0.18115942028985507</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>777</v>
       </c>
@@ -920,8 +1067,24 @@
         <f t="shared" si="1"/>
         <v>0.16473616473616473</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q8">
+        <f t="shared" si="2"/>
+        <v>0.98113207547169812</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="3"/>
+        <v>0.16275430359937401</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="4"/>
+        <v>0.25263157894736843</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="5"/>
+        <v>0.17391304347826086</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>777</v>
       </c>
@@ -967,8 +1130,24 @@
         <f t="shared" si="1"/>
         <v>0.40669240669240669</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q9">
+        <f t="shared" si="2"/>
+        <v>0.98310810810810811</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="3"/>
+        <v>0.45539906103286387</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="4"/>
+        <v>0.23809523809523808</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="5"/>
+        <v>0.18115942028985507</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>777</v>
       </c>
@@ -1007,15 +1186,31 @@
       </c>
       <c r="M10" s="4"/>
       <c r="N10" s="7">
-        <f t="shared" ref="N10:N11" si="2">G10/E10</f>
+        <f t="shared" ref="N10:N11" si="6">G10/E10</f>
         <v>0.83114035087719296</v>
       </c>
       <c r="O10" s="7">
-        <f t="shared" ref="O10:O11" si="3">G10/A10</f>
+        <f t="shared" ref="O10:O11" si="7">G10/A10</f>
         <v>0.48777348777348778</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q10">
+        <f t="shared" si="2"/>
+        <v>0.99150141643059486</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="3"/>
+        <v>0.54773082942097029</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="4"/>
+        <v>0.27619047619047621</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="5"/>
+        <v>0.21014492753623187</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>777</v>
       </c>
@@ -1054,15 +1249,31 @@
       </c>
       <c r="M11" s="4"/>
       <c r="N11" s="7">
+        <f t="shared" si="6"/>
+        <v>0.67169811320754713</v>
+      </c>
+      <c r="O11" s="7">
+        <f t="shared" si="7"/>
+        <v>0.22908622908622908</v>
+      </c>
+      <c r="Q11">
         <f t="shared" si="2"/>
-        <v>0.67169811320754713</v>
-      </c>
-      <c r="O11" s="7">
+        <v>0.98026315789473684</v>
+      </c>
+      <c r="R11">
         <f t="shared" si="3"/>
-        <v>0.22908622908622908</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" s="8" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+        <v>0.23317683881064163</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="4"/>
+        <v>0.25663716814159293</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="5"/>
+        <v>0.21014492753623187</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" s="8" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B12" s="9">
         <v>1331</v>
       </c>
@@ -1108,24 +1319,154 @@
         <f>AVERAGE(O2:O11)</f>
         <v>0.39021879021879019</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="84" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="85" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="86" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="87" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="88" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="89" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="90" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="91" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="92" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="93" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="94" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="95" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="96" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="97" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
+      <c r="Q12" s="18">
+        <f t="shared" ref="Q12:R12" si="8">AVERAGE(Q2:Q11)</f>
+        <v>0.98492062830107641</v>
+      </c>
+      <c r="R12" s="18">
+        <f t="shared" si="8"/>
+        <v>0.43270735524256654</v>
+      </c>
+      <c r="S12"/>
+      <c r="T12" s="18">
+        <f t="shared" ref="T12:U12" si="9">AVERAGE(T2:T11)</f>
+        <v>0.25704668324666907</v>
+      </c>
+      <c r="U12" s="18">
+        <f t="shared" si="9"/>
+        <v>0.19347826086956518</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="J13" s="20">
+        <f>J12+K12</f>
+        <v>280.60000000000002</v>
+      </c>
+      <c r="L13" s="20">
+        <f>I12+L12</f>
+        <v>103.9</v>
+      </c>
+      <c r="Q13"/>
+      <c r="R13"/>
+      <c r="S13"/>
+      <c r="T13"/>
+      <c r="U13"/>
+    </row>
+    <row r="14" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q14"/>
+      <c r="R14"/>
+      <c r="S14"/>
+      <c r="T14"/>
+      <c r="U14"/>
+    </row>
+    <row r="15" spans="1:21" s="2" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A15" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q15"/>
+      <c r="R15"/>
+      <c r="S15"/>
+      <c r="T15"/>
+      <c r="U15"/>
+    </row>
+    <row r="84" spans="17:21" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q84"/>
+      <c r="R84"/>
+      <c r="S84"/>
+      <c r="T84"/>
+      <c r="U84"/>
+    </row>
+    <row r="85" spans="17:21" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q85"/>
+      <c r="R85"/>
+      <c r="S85"/>
+      <c r="T85"/>
+      <c r="U85"/>
+    </row>
+    <row r="86" spans="17:21" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q86"/>
+      <c r="R86"/>
+      <c r="S86"/>
+      <c r="T86"/>
+      <c r="U86"/>
+    </row>
+    <row r="87" spans="17:21" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q87"/>
+      <c r="R87"/>
+      <c r="S87"/>
+      <c r="T87"/>
+      <c r="U87"/>
+    </row>
+    <row r="88" spans="17:21" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q88"/>
+      <c r="R88"/>
+      <c r="S88"/>
+      <c r="T88"/>
+      <c r="U88"/>
+    </row>
+    <row r="89" spans="17:21" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q89"/>
+      <c r="R89"/>
+      <c r="S89"/>
+      <c r="T89"/>
+      <c r="U89"/>
+    </row>
+    <row r="90" spans="17:21" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q90"/>
+      <c r="R90"/>
+      <c r="S90"/>
+      <c r="T90"/>
+      <c r="U90"/>
+    </row>
+    <row r="91" spans="17:21" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q91"/>
+      <c r="R91"/>
+      <c r="S91"/>
+      <c r="T91"/>
+      <c r="U91"/>
+    </row>
+    <row r="92" spans="17:21" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q92"/>
+      <c r="R92"/>
+      <c r="S92"/>
+      <c r="T92"/>
+      <c r="U92"/>
+    </row>
+    <row r="93" spans="17:21" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q93"/>
+      <c r="R93"/>
+      <c r="S93"/>
+      <c r="T93"/>
+      <c r="U93"/>
+    </row>
+    <row r="94" spans="17:21" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q94"/>
+      <c r="R94"/>
+      <c r="S94"/>
+      <c r="T94"/>
+      <c r="U94"/>
+    </row>
+    <row r="95" spans="17:21" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q95"/>
+      <c r="R95"/>
+      <c r="S95"/>
+      <c r="T95"/>
+      <c r="U95"/>
+    </row>
+    <row r="96" spans="17:21" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q96"/>
+      <c r="R96"/>
+      <c r="S96"/>
+      <c r="T96"/>
+      <c r="U96"/>
+    </row>
+    <row r="97" spans="17:21" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q97"/>
+      <c r="R97"/>
+      <c r="S97"/>
+      <c r="T97"/>
+      <c r="U97"/>
+    </row>
   </sheetData>
   <pageMargins left="0.78750000000000009" right="0.78750000000000009" top="1.0249999999999997" bottom="1.0249999999999997" header="0.78750000000000009" footer="0.78750000000000009"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
@@ -1138,14 +1479,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="1" customWidth="1"/>
-    <col min="2" max="16384" width="12.6640625" style="1"/>
+    <col min="2" max="16" width="12.6640625" style="1"/>
+    <col min="22" max="16384" width="12.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1189,8 +1531,20 @@
       <c r="O1" s="5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q1" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>777</v>
       </c>
@@ -1236,8 +1590,24 @@
         <f t="shared" ref="O2:O9" si="1">G2/A2</f>
         <v>0.58172458172458175</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q2">
+        <f>J2/(J2+K2)</f>
+        <v>0.98062953995157387</v>
+      </c>
+      <c r="R2">
+        <f>J2/639</f>
+        <v>0.63380281690140849</v>
+      </c>
+      <c r="T2">
+        <f>I2/(I2+L2)</f>
+        <v>0.27167630057803466</v>
+      </c>
+      <c r="U2">
+        <f>I2/138</f>
+        <v>0.34057971014492755</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>777</v>
       </c>
@@ -1283,8 +1653,24 @@
         <f t="shared" si="1"/>
         <v>0.60102960102960101</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q3">
+        <f t="shared" ref="Q3:Q11" si="2">J3/(J3+K3)</f>
+        <v>0.97931034482758617</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R11" si="3">J3/639</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="T3">
+        <f t="shared" ref="T3:T11" si="4">I3/(I3+L3)</f>
+        <v>0.25624999999999998</v>
+      </c>
+      <c r="U3">
+        <f t="shared" ref="U3:U11" si="5">I3/138</f>
+        <v>0.29710144927536231</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>777</v>
       </c>
@@ -1330,8 +1716,24 @@
         <f t="shared" si="1"/>
         <v>0.62676962676962678</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q4">
+        <f t="shared" si="2"/>
+        <v>0.97972972972972971</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="3"/>
+        <v>0.68075117370892024</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="4"/>
+        <v>0.26804123711340205</v>
+      </c>
+      <c r="U4">
+        <f>I4/138</f>
+        <v>0.37681159420289856</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>777</v>
       </c>
@@ -1377,8 +1779,24 @@
         <f t="shared" si="1"/>
         <v>0.62419562419562424</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q5">
+        <f t="shared" si="2"/>
+        <v>0.97977528089887644</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="3"/>
+        <v>0.68231611893583721</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="4"/>
+        <v>0.24873096446700507</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="5"/>
+        <v>0.35507246376811596</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>777</v>
       </c>
@@ -1424,8 +1842,24 @@
         <f t="shared" si="1"/>
         <v>0.63191763191763195</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q6">
+        <f t="shared" si="2"/>
+        <v>0.98</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="3"/>
+        <v>0.6901408450704225</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="4"/>
+        <v>0.26455026455026454</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="5"/>
+        <v>0.36231884057971014</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>777</v>
       </c>
@@ -1471,8 +1905,24 @@
         <f t="shared" si="1"/>
         <v>0.62419562419562424</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q7">
+        <f t="shared" si="2"/>
+        <v>0.98633257403189067</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="3"/>
+        <v>0.67762128325508608</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="4"/>
+        <v>0.27659574468085107</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="5"/>
+        <v>0.37681159420289856</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>777</v>
       </c>
@@ -1518,8 +1968,24 @@
         <f t="shared" si="1"/>
         <v>0.54697554697554696</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q8">
+        <f t="shared" si="2"/>
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="3"/>
+        <v>0.58841940532081383</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="4"/>
+        <v>0.2832369942196532</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="5"/>
+        <v>0.35507246376811596</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>777</v>
       </c>
@@ -1565,8 +2031,24 @@
         <f t="shared" si="1"/>
         <v>0.6357786357786358</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q9">
+        <f t="shared" si="2"/>
+        <v>0.97986577181208057</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="3"/>
+        <v>0.68544600938967137</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="4"/>
+        <v>0.27184466019417475</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="5"/>
+        <v>0.40579710144927539</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>777</v>
       </c>
@@ -1605,15 +2087,31 @@
       </c>
       <c r="M10" s="4"/>
       <c r="N10" s="7">
-        <f t="shared" ref="N10:N11" si="2">G10/E10</f>
+        <f t="shared" ref="N10:N11" si="6">G10/E10</f>
         <v>0.77616747181964574</v>
       </c>
       <c r="O10" s="7">
-        <f t="shared" ref="O10:O11" si="3">G10/A10</f>
+        <f t="shared" ref="O10:O11" si="7">G10/A10</f>
         <v>0.62033462033462028</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q10">
+        <f t="shared" si="2"/>
+        <v>0.99078341013824889</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="3"/>
+        <v>0.67292644757433495</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="4"/>
+        <v>0.27807486631016043</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="5"/>
+        <v>0.37681159420289856</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>777</v>
       </c>
@@ -1652,15 +2150,31 @@
       </c>
       <c r="M11" s="4"/>
       <c r="N11" s="7">
+        <f t="shared" si="6"/>
+        <v>0.75</v>
+      </c>
+      <c r="O11" s="7">
+        <f t="shared" si="7"/>
+        <v>0.56756756756756754</v>
+      </c>
+      <c r="Q11">
         <f t="shared" si="2"/>
-        <v>0.75</v>
-      </c>
-      <c r="O11" s="7">
+        <v>0.98209718670076729</v>
+      </c>
+      <c r="R11">
         <f t="shared" si="3"/>
-        <v>0.56756756756756754</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+        <v>0.60093896713615025</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="4"/>
+        <v>0.28934010152284262</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="5"/>
+        <v>0.41304347826086957</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="13"/>
       <c r="B12" s="9">
         <v>1331</v>
@@ -1708,6 +2222,37 @@
         <f>AVERAGE(O2:O11)</f>
         <v>0.60604890604890604</v>
       </c>
+      <c r="Q12" s="18">
+        <f t="shared" ref="Q12:R12" si="8">AVERAGE(Q2:Q11)</f>
+        <v>0.98176905047574192</v>
+      </c>
+      <c r="R12" s="18">
+        <f t="shared" si="8"/>
+        <v>0.65790297339593107</v>
+      </c>
+      <c r="T12" s="18">
+        <f t="shared" ref="T12:U12" si="9">AVERAGE(T2:T11)</f>
+        <v>0.27083411336363883</v>
+      </c>
+      <c r="U12" s="18">
+        <f t="shared" si="9"/>
+        <v>0.36594202898550726</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="J13" s="20">
+        <f>J12+K12</f>
+        <v>428.2</v>
+      </c>
+      <c r="L13" s="20">
+        <f>I12+L12</f>
+        <v>186.4</v>
+      </c>
+      <c r="Q13"/>
+      <c r="R13"/>
+      <c r="S13"/>
+      <c r="T13"/>
+      <c r="U13"/>
     </row>
   </sheetData>
   <pageMargins left="0.78750000000000009" right="0.78750000000000009" top="1.0249999999999997" bottom="1.0249999999999997" header="0.78750000000000009" footer="0.78750000000000009"/>
@@ -1721,14 +2266,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="1" customWidth="1"/>
-    <col min="2" max="16384" width="12.6640625" style="1"/>
+    <col min="2" max="16" width="12.6640625" style="1"/>
+    <col min="22" max="16384" width="12.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
@@ -1772,8 +2318,20 @@
       <c r="O1" s="5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q1" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>777</v>
       </c>
@@ -1819,8 +2377,24 @@
         <f t="shared" ref="O2:O9" si="1">G2/A2</f>
         <v>0.65379665379665375</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q2">
+        <f>J2/(J2+K2)</f>
+        <v>0.98185941043083902</v>
+      </c>
+      <c r="R2">
+        <f>J2/639</f>
+        <v>0.67762128325508608</v>
+      </c>
+      <c r="T2">
+        <f>I2/(I2+L2)</f>
+        <v>0.27573529411764708</v>
+      </c>
+      <c r="U2">
+        <f>I2/138</f>
+        <v>0.54347826086956519</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>777</v>
       </c>
@@ -1866,8 +2440,24 @@
         <f t="shared" si="1"/>
         <v>0.64607464607464604</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q3">
+        <f t="shared" ref="Q3:Q11" si="2">J3/(J3+K3)</f>
+        <v>0.99310344827586206</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R11" si="3">J3/639</f>
+        <v>0.676056338028169</v>
+      </c>
+      <c r="T3">
+        <f t="shared" ref="T3:T11" si="4">I3/(I3+L3)</f>
+        <v>0.26415094339622641</v>
+      </c>
+      <c r="U3">
+        <f t="shared" ref="U3:U11" si="5">I3/138</f>
+        <v>0.50724637681159424</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>777</v>
       </c>
@@ -1913,8 +2503,24 @@
         <f t="shared" si="1"/>
         <v>0.67052767052767048</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q4">
+        <f t="shared" si="2"/>
+        <v>0.98017621145374445</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="3"/>
+        <v>0.69640062597809071</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="4"/>
+        <v>0.24836601307189543</v>
+      </c>
+      <c r="U4">
+        <f>I4/138</f>
+        <v>0.55072463768115942</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>777</v>
       </c>
@@ -1960,8 +2566,24 @@
         <f t="shared" si="1"/>
         <v>0.66795366795366795</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q5">
+        <f t="shared" si="2"/>
+        <v>0.98013245033112584</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="3"/>
+        <v>0.69483568075117375</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="4"/>
+        <v>0.25510204081632654</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="5"/>
+        <v>0.54347826086956519</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>777</v>
       </c>
@@ -2007,8 +2629,24 @@
         <f t="shared" si="1"/>
         <v>0.66151866151866157</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q6">
+        <f t="shared" si="2"/>
+        <v>0.98026315789473684</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="3"/>
+        <v>0.69953051643192488</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="4"/>
+        <v>0.25378787878787878</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="5"/>
+        <v>0.48550724637681159</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>777</v>
       </c>
@@ -2054,8 +2692,24 @@
         <f t="shared" si="1"/>
         <v>0.66023166023166024</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q7">
+        <f t="shared" si="2"/>
+        <v>0.98008849557522126</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="3"/>
+        <v>0.69327073552425666</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="4"/>
+        <v>0.24911032028469751</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="5"/>
+        <v>0.50724637681159424</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>777</v>
       </c>
@@ -2101,8 +2755,24 @@
         <f t="shared" si="1"/>
         <v>0.63706563706563701</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q8">
+        <f t="shared" si="2"/>
+        <v>0.97935779816513757</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="3"/>
+        <v>0.66823161189358371</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="4"/>
+        <v>0.26053639846743293</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="5"/>
+        <v>0.49275362318840582</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>777</v>
       </c>
@@ -2148,8 +2818,24 @@
         <f t="shared" si="1"/>
         <v>0.67052767052767048</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q9">
+        <f t="shared" si="2"/>
+        <v>0.98</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="3"/>
+        <v>0.6901408450704225</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="4"/>
+        <v>0.26058631921824105</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="5"/>
+        <v>0.57971014492753625</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>777</v>
       </c>
@@ -2188,15 +2874,31 @@
       </c>
       <c r="M10" s="4"/>
       <c r="N10" s="7">
-        <f t="shared" ref="N10:N11" si="2">G10/E10</f>
+        <f t="shared" ref="N10:N11" si="6">G10/E10</f>
         <v>0.693029490616622</v>
       </c>
       <c r="O10" s="7">
-        <f t="shared" ref="O10:O11" si="3">G10/A10</f>
+        <f t="shared" ref="O10:O11" si="7">G10/A10</f>
         <v>0.66537966537966542</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q10">
+        <f t="shared" si="2"/>
+        <v>0.98</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="3"/>
+        <v>0.6901408450704225</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="4"/>
+        <v>0.25675675675675674</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="5"/>
+        <v>0.55072463768115942</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>777</v>
       </c>
@@ -2235,15 +2937,31 @@
       </c>
       <c r="M11" s="4"/>
       <c r="N11" s="7">
+        <f t="shared" si="6"/>
+        <v>0.68698060941828254</v>
+      </c>
+      <c r="O11" s="7">
+        <f t="shared" si="7"/>
+        <v>0.63835263835263834</v>
+      </c>
+      <c r="Q11">
         <f t="shared" si="2"/>
-        <v>0.68698060941828254</v>
-      </c>
-      <c r="O11" s="7">
+        <v>0.9814385150812065</v>
+      </c>
+      <c r="R11">
         <f t="shared" si="3"/>
-        <v>0.63835263835263834</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+        <v>0.6619718309859155</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="4"/>
+        <v>0.25085910652920962</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="5"/>
+        <v>0.52898550724637683</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="13"/>
       <c r="B12" s="9">
         <v>1331</v>
@@ -2291,6 +3009,37 @@
         <f>AVERAGE(O2:O11)</f>
         <v>0.65714285714285725</v>
       </c>
+      <c r="Q12" s="18">
+        <f t="shared" ref="Q12:R12" si="8">AVERAGE(Q2:Q11)</f>
+        <v>0.98164194872078736</v>
+      </c>
+      <c r="R12" s="18">
+        <f t="shared" si="8"/>
+        <v>0.68482003129890445</v>
+      </c>
+      <c r="T12" s="18">
+        <f t="shared" ref="T12:U12" si="9">AVERAGE(T2:T11)</f>
+        <v>0.2574991071446312</v>
+      </c>
+      <c r="U12" s="18">
+        <f t="shared" si="9"/>
+        <v>0.52898550724637672</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="J13" s="20">
+        <f>J12+K12</f>
+        <v>445.8</v>
+      </c>
+      <c r="L13" s="20">
+        <f>I12+L12</f>
+        <v>283.7</v>
+      </c>
+      <c r="Q13"/>
+      <c r="R13"/>
+      <c r="S13"/>
+      <c r="T13"/>
+      <c r="U13"/>
     </row>
   </sheetData>
   <pageMargins left="0.78750000000000009" right="0.78750000000000009" top="1.0249999999999997" bottom="1.0249999999999997" header="0.78750000000000009" footer="0.78750000000000009"/>
@@ -2304,13 +3053,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:U15"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="12.6640625" style="1"/>
+    <col min="1" max="16" width="12.6640625" style="1"/>
+    <col min="22" max="16384" width="12.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
@@ -2354,8 +3104,20 @@
       <c r="O1" s="5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q1" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>1851</v>
       </c>
@@ -2401,8 +3163,24 @@
         <f t="shared" ref="O2:O9" si="1">G2/A2</f>
         <v>0.22204213938411668</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q2">
+        <f>J2/(J2+K2)</f>
+        <v>0.99189189189189186</v>
+      </c>
+      <c r="R2">
+        <f>J2/1727</f>
+        <v>0.212507237984945</v>
+      </c>
+      <c r="T2">
+        <f>I2/(I2+L2)</f>
+        <v>0.25882352941176473</v>
+      </c>
+      <c r="U2">
+        <f>I2/124</f>
+        <v>0.35483870967741937</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>1851</v>
       </c>
@@ -2448,8 +3226,24 @@
         <f t="shared" si="1"/>
         <v>0.34089681253376553</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q3">
+        <f t="shared" ref="Q3:Q11" si="2">J3/(J3+K3)</f>
+        <v>0.99327731092436977</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R11" si="3">J3/1727</f>
+        <v>0.34221192819918933</v>
+      </c>
+      <c r="T3">
+        <f t="shared" ref="T3:T11" si="4">I3/(I3+L3)</f>
+        <v>0.2484472049689441</v>
+      </c>
+      <c r="U3">
+        <f t="shared" ref="U3:U11" si="5">I3/124</f>
+        <v>0.32258064516129031</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>1851</v>
       </c>
@@ -2495,8 +3289,24 @@
         <f t="shared" si="1"/>
         <v>0.42517558076715289</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q4">
+        <f t="shared" si="2"/>
+        <v>0.98280423280423279</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="3"/>
+        <v>0.43022582513028373</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="4"/>
+        <v>0.25433526011560692</v>
+      </c>
+      <c r="U4">
+        <f t="shared" si="5"/>
+        <v>0.35483870967741937</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>1851</v>
       </c>
@@ -2542,8 +3352,24 @@
         <f t="shared" si="1"/>
         <v>0.32306861156131822</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q5">
+        <f t="shared" si="2"/>
+        <v>0.98926654740608233</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="3"/>
+        <v>0.32020845396641573</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="4"/>
+        <v>0.26470588235294118</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="5"/>
+        <v>0.36290322580645162</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>1851</v>
       </c>
@@ -2589,8 +3415,24 @@
         <f t="shared" si="1"/>
         <v>0.25877903835764454</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q6">
+        <f t="shared" si="2"/>
+        <v>0.99099099099099097</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="3"/>
+        <v>0.25477707006369427</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="4"/>
+        <v>0.26174496644295303</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="5"/>
+        <v>0.31451612903225806</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>1851</v>
       </c>
@@ -2636,8 +3478,24 @@
         <f t="shared" si="1"/>
         <v>0.26526202052944353</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q7">
+        <f t="shared" si="2"/>
+        <v>0.98684210526315785</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="3"/>
+        <v>0.26056745801968734</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="4"/>
+        <v>0.27702702702702703</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="5"/>
+        <v>0.33064516129032256</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>1851</v>
       </c>
@@ -2683,8 +3541,24 @@
         <f t="shared" si="1"/>
         <v>0.24743381955699623</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q8">
+        <f t="shared" si="2"/>
+        <v>0.99047619047619051</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="3"/>
+        <v>0.24088013896931093</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="4"/>
+        <v>0.26582278481012656</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="5"/>
+        <v>0.33870967741935482</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>1851</v>
       </c>
@@ -2730,8 +3604,24 @@
         <f t="shared" si="1"/>
         <v>0.37817396002160997</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q9">
+        <f t="shared" si="2"/>
+        <v>0.98789712556732223</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="3"/>
+        <v>0.37811233352634627</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="4"/>
+        <v>0.27810650887573962</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="5"/>
+        <v>0.37903225806451613</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>1851</v>
       </c>
@@ -2770,15 +3660,31 @@
       </c>
       <c r="M10" s="4"/>
       <c r="N10" s="7">
-        <f t="shared" ref="N10:N11" si="2">G10/E10</f>
+        <f t="shared" ref="N10:N11" si="6">G10/E10</f>
         <v>0.82896551724137935</v>
       </c>
       <c r="O10" s="7">
-        <f t="shared" ref="O10:O11" si="3">G10/A10</f>
+        <f t="shared" ref="O10:O11" si="7">G10/A10</f>
         <v>0.32468935710426794</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q10">
+        <f t="shared" si="2"/>
+        <v>0.98594024604569419</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="3"/>
+        <v>0.32484076433121017</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="4"/>
+        <v>0.25641025641025639</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="5"/>
+        <v>0.32258064516129031</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>1851</v>
       </c>
@@ -2817,15 +3723,31 @@
       </c>
       <c r="M11" s="4"/>
       <c r="N11" s="7">
+        <f t="shared" si="6"/>
+        <v>0.79039999999999999</v>
+      </c>
+      <c r="O11" s="7">
+        <f t="shared" si="7"/>
+        <v>0.26688276607239331</v>
+      </c>
+      <c r="Q11">
         <f t="shared" si="2"/>
-        <v>0.79039999999999999</v>
-      </c>
-      <c r="O11" s="7">
+        <v>0.98901098901098905</v>
+      </c>
+      <c r="R11">
         <f t="shared" si="3"/>
-        <v>0.26688276607239331</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+        <v>0.26056745801968734</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="4"/>
+        <v>0.25882352941176473</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="5"/>
+        <v>0.35483870967741937</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="13"/>
       <c r="B12" s="9">
         <v>1331</v>
@@ -2872,6 +3794,42 @@
       <c r="O12" s="12">
         <f>AVERAGE(O2:O11)</f>
         <v>0.30524041058887091</v>
+      </c>
+      <c r="Q12" s="18">
+        <f t="shared" ref="Q12:R12" si="8">AVERAGE(Q2:Q11)</f>
+        <v>0.98883976303809207</v>
+      </c>
+      <c r="R12" s="18">
+        <f t="shared" si="8"/>
+        <v>0.30248986682107704</v>
+      </c>
+      <c r="T12" s="18">
+        <f t="shared" ref="T12:U12" si="9">AVERAGE(T2:T11)</f>
+        <v>0.26242469498271237</v>
+      </c>
+      <c r="U12" s="18">
+        <f t="shared" si="9"/>
+        <v>0.34354838709677421</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="J13" s="20">
+        <f>J12+K12</f>
+        <v>528.5</v>
+      </c>
+      <c r="L13" s="20">
+        <f>I12+L12</f>
+        <v>162.4</v>
+      </c>
+      <c r="Q13"/>
+      <c r="R13"/>
+      <c r="S13"/>
+      <c r="T13"/>
+      <c r="U13"/>
+    </row>
+    <row r="15" spans="1:21" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A15" s="19" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -2886,14 +3844,15 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="1" customWidth="1"/>
-    <col min="2" max="16384" width="12.6640625" style="1"/>
+    <col min="2" max="16" width="12.6640625" style="1"/>
+    <col min="22" max="16384" width="12.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
@@ -2937,8 +3896,20 @@
       <c r="O1" s="5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q1" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>1851</v>
       </c>
@@ -2984,8 +3955,24 @@
         <f t="shared" ref="O2:O9" si="1">G2/A2</f>
         <v>0.45596974608319829</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q2">
+        <f>J2/(J2+K2)</f>
+        <v>0.98337595907928388</v>
+      </c>
+      <c r="R2">
+        <f>J2/1727</f>
+        <v>0.44528083381586564</v>
+      </c>
+      <c r="T2">
+        <f>I2/(I2+L2)</f>
+        <v>0.22058823529411764</v>
+      </c>
+      <c r="U2">
+        <f>I2/124</f>
+        <v>0.60483870967741937</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>1851</v>
       </c>
@@ -3031,8 +4018,24 @@
         <f t="shared" si="1"/>
         <v>0.62668827660723936</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q3">
+        <f t="shared" ref="Q3:Q11" si="2">J3/(J3+K3)</f>
+        <v>0.97845601436265706</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R11" si="3">J3/1727</f>
+        <v>0.63115228720324257</v>
+      </c>
+      <c r="T3">
+        <f t="shared" ref="T3:T11" si="4">I3/(I3+L3)</f>
+        <v>0.23411371237458195</v>
+      </c>
+      <c r="U3">
+        <f t="shared" ref="U3:U11" si="5">I3/124</f>
+        <v>0.56451612903225812</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>1851</v>
       </c>
@@ -3078,8 +4081,24 @@
         <f t="shared" si="1"/>
         <v>0.68719611021069693</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q4">
+        <f t="shared" si="2"/>
+        <v>0.97558991049633847</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="3"/>
+        <v>0.69426751592356684</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="4"/>
+        <v>0.22741433021806853</v>
+      </c>
+      <c r="U4">
+        <f t="shared" si="5"/>
+        <v>0.58870967741935487</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>1851</v>
       </c>
@@ -3125,8 +4144,24 @@
         <f t="shared" si="1"/>
         <v>0.54727174500270126</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q5">
+        <f t="shared" si="2"/>
+        <v>0.98219895287958114</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="3"/>
+        <v>0.54313839027214827</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="4"/>
+        <v>0.24752475247524752</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="5"/>
+        <v>0.60483870967741937</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>1851</v>
       </c>
@@ -3172,8 +4207,24 @@
         <f t="shared" si="1"/>
         <v>0.5083738519719071</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q6">
+        <f t="shared" si="2"/>
+        <v>0.98421645997745211</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="3"/>
+        <v>0.50550086855819343</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="4"/>
+        <v>0.23367697594501718</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="5"/>
+        <v>0.54838709677419351</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>1851</v>
       </c>
@@ -3219,8 +4270,24 @@
         <f t="shared" si="1"/>
         <v>0.57698541329011344</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q7">
+        <f t="shared" si="2"/>
+        <v>0.97941176470588232</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="3"/>
+        <v>0.57845975680370587</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="4"/>
+        <v>0.2363013698630137</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="5"/>
+        <v>0.55645161290322576</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>1851</v>
       </c>
@@ -3266,8 +4333,24 @@
         <f t="shared" si="1"/>
         <v>0.56185845488924901</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q8">
+        <f t="shared" si="2"/>
+        <v>0.98268839103869654</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="3"/>
+        <v>0.55877243775332952</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="4"/>
+        <v>0.22658610271903323</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="5"/>
+        <v>0.60483870967741937</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>1851</v>
       </c>
@@ -3313,8 +4396,24 @@
         <f t="shared" si="1"/>
         <v>0.65586169638033498</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q9">
+        <f t="shared" si="2"/>
+        <v>0.97773972602739723</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="3"/>
+        <v>0.66126230457440649</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="4"/>
+        <v>0.22570532915360503</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="5"/>
+        <v>0.58064516129032262</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>1851</v>
       </c>
@@ -3353,15 +4452,31 @@
       </c>
       <c r="M10" s="4"/>
       <c r="N10" s="7">
-        <f t="shared" ref="N10:N11" si="2">G10/E10</f>
+        <f t="shared" ref="N10:N11" si="6">G10/E10</f>
         <v>0.82229508196721313</v>
       </c>
       <c r="O10" s="7">
-        <f t="shared" ref="O10:O11" si="3">G10/A10</f>
+        <f t="shared" ref="O10:O11" si="7">G10/A10</f>
         <v>0.67747163695299839</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q10">
+        <f t="shared" si="2"/>
+        <v>0.97674418604651159</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="3"/>
+        <v>0.68094962362478284</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="4"/>
+        <v>0.24299065420560748</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="5"/>
+        <v>0.62903225806451613</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>1851</v>
       </c>
@@ -3400,15 +4515,31 @@
       </c>
       <c r="M11" s="4"/>
       <c r="N11" s="7">
+        <f t="shared" si="6"/>
+        <v>0.7978227060653188</v>
+      </c>
+      <c r="O11" s="7">
+        <f t="shared" si="7"/>
+        <v>0.5542949756888168</v>
+      </c>
+      <c r="Q11">
         <f t="shared" si="2"/>
-        <v>0.7978227060653188</v>
-      </c>
-      <c r="O11" s="7">
+        <v>0.98047276464542654</v>
+      </c>
+      <c r="R11">
         <f t="shared" si="3"/>
-        <v>0.5542949756888168</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+        <v>0.55240301100173717</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="4"/>
+        <v>0.23003194888178913</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="5"/>
+        <v>0.58064516129032262</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="13"/>
       <c r="B12" s="9">
         <v>1331</v>
@@ -3458,6 +4589,37 @@
         <f>AVERAGE(O2:O11)</f>
         <v>0.58519719070772547</v>
       </c>
+      <c r="Q12" s="18">
+        <f t="shared" ref="Q12:R12" si="8">AVERAGE(Q2:Q11)</f>
+        <v>0.98008941292592267</v>
+      </c>
+      <c r="R12" s="18">
+        <f t="shared" si="8"/>
+        <v>0.58511870295309787</v>
+      </c>
+      <c r="T12" s="18">
+        <f t="shared" ref="T12:U12" si="9">AVERAGE(T2:T11)</f>
+        <v>0.23249334111300812</v>
+      </c>
+      <c r="U12" s="18">
+        <f t="shared" si="9"/>
+        <v>0.58629032258064517</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="J13" s="20">
+        <f>J12+K12</f>
+        <v>1031.4000000000001</v>
+      </c>
+      <c r="L13" s="20">
+        <f>I12+L12</f>
+        <v>313</v>
+      </c>
+      <c r="Q13"/>
+      <c r="R13"/>
+      <c r="S13"/>
+      <c r="T13"/>
+      <c r="U13"/>
     </row>
   </sheetData>
   <pageMargins left="0.78750000000000009" right="0.78750000000000009" top="1.0249999999999997" bottom="1.0249999999999997" header="0.78750000000000009" footer="0.78750000000000009"/>
@@ -3471,17 +4633,18 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="1" customWidth="1"/>
     <col min="2" max="12" width="12.6640625" style="1"/>
     <col min="13" max="13" width="16.77734375" style="1" customWidth="1"/>
     <col min="15" max="15" width="12.6640625" style="2"/>
-    <col min="16" max="16384" width="12.6640625" style="1"/>
+    <col min="16" max="16" width="12.6640625" style="1"/>
+    <col min="22" max="16384" width="12.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
@@ -3525,8 +4688,20 @@
       <c r="O1" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q1" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>1851</v>
       </c>
@@ -3572,8 +4747,24 @@
         <f t="shared" ref="O2:O9" si="1">G2/A2</f>
         <v>0.62776877363587247</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q2">
+        <f>J2/(J2+K2)</f>
+        <v>0.97704315886134063</v>
+      </c>
+      <c r="R2">
+        <f>J2/1727</f>
+        <v>0.61609727851766072</v>
+      </c>
+      <c r="T2">
+        <f>I2/(I2+L2)</f>
+        <v>0.19878296146044624</v>
+      </c>
+      <c r="U2">
+        <f>I2/124</f>
+        <v>0.79032258064516125</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>1851</v>
       </c>
@@ -3619,8 +4810,24 @@
         <f t="shared" si="1"/>
         <v>0.78390059427336578</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q3">
+        <f t="shared" ref="Q3:Q11" si="2">J3/(J3+K3)</f>
+        <v>0.97208303507516103</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R11" si="3">J3/1727</f>
+        <v>0.78633468442385634</v>
+      </c>
+      <c r="T3">
+        <f t="shared" ref="T3:T11" si="4">I3/(I3+L3)</f>
+        <v>0.21428571428571427</v>
+      </c>
+      <c r="U3">
+        <f t="shared" ref="U3:U11" si="5">I3/124</f>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>1851</v>
       </c>
@@ -3666,8 +4873,24 @@
         <f t="shared" si="1"/>
         <v>0.81685575364667751</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q4">
+        <f t="shared" si="2"/>
+        <v>0.97056810403832994</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="3"/>
+        <v>0.82107701215981466</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="4"/>
+        <v>0.20982142857142858</v>
+      </c>
+      <c r="U4">
+        <f t="shared" si="5"/>
+        <v>0.75806451612903225</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>1851</v>
       </c>
@@ -3713,8 +4936,24 @@
         <f t="shared" si="1"/>
         <v>0.72339276066990821</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q5">
+        <f t="shared" si="2"/>
+        <v>0.97337509788566956</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="3"/>
+        <v>0.71974522292993626</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="4"/>
+        <v>0.22119815668202766</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="5"/>
+        <v>0.77419354838709675</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>1851</v>
       </c>
@@ -3760,8 +4999,24 @@
         <f t="shared" si="1"/>
         <v>0.72123176661264177</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q6">
+        <f t="shared" si="2"/>
+        <v>0.97488226059654626</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="3"/>
+        <v>0.71916618413433697</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="4"/>
+        <v>0.20217391304347826</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="5"/>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>1851</v>
       </c>
@@ -3807,8 +5062,24 @@
         <f t="shared" si="1"/>
         <v>0.74878444084278772</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q7">
+        <f t="shared" si="2"/>
+        <v>0.97364457831325302</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="3"/>
+        <v>0.74869716270990161</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="4"/>
+        <v>0.21088435374149661</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="5"/>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>1851</v>
       </c>
@@ -3854,8 +5125,24 @@
         <f t="shared" si="1"/>
         <v>0.73095623987034031</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q8">
+        <f t="shared" si="2"/>
+        <v>0.9728892331525949</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="3"/>
+        <v>0.72727272727272729</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="4"/>
+        <v>0.19635627530364372</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="5"/>
+        <v>0.782258064516129</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>1851</v>
       </c>
@@ -3901,8 +5188,24 @@
         <f t="shared" si="1"/>
         <v>0.84927066450567257</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q9">
+        <f t="shared" si="2"/>
+        <v>0.97039473684210531</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="3"/>
+        <v>0.85408222350897511</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="4"/>
+        <v>0.19755600814663951</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="5"/>
+        <v>0.782258064516129</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>1851</v>
       </c>
@@ -3941,15 +5244,31 @@
       </c>
       <c r="M10" s="4"/>
       <c r="N10">
-        <f t="shared" ref="N10:N11" si="2">G10/E10</f>
+        <f t="shared" ref="N10:N11" si="6">G10/E10</f>
         <v>0.78801843317972353</v>
       </c>
       <c r="O10" s="2">
-        <f t="shared" ref="O10:O11" si="3">G10/A10</f>
+        <f t="shared" ref="O10:O11" si="7">G10/A10</f>
         <v>0.83144246353322526</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Q10">
+        <f t="shared" si="2"/>
+        <v>0.97043010752688175</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="3"/>
+        <v>0.83613202084539662</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="4"/>
+        <v>0.20430107526881722</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="5"/>
+        <v>0.7661290322580645</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>1851</v>
       </c>
@@ -3988,15 +5307,31 @@
       </c>
       <c r="M11" s="4"/>
       <c r="N11">
+        <f t="shared" si="6"/>
+        <v>0.77728776185226023</v>
+      </c>
+      <c r="O11" s="2">
+        <f t="shared" si="7"/>
+        <v>0.7617504051863857</v>
+      </c>
+      <c r="Q11">
         <f t="shared" si="2"/>
-        <v>0.77728776185226023</v>
-      </c>
-      <c r="O11" s="2">
+        <v>0.97255192878338281</v>
+      </c>
+      <c r="R11">
         <f t="shared" si="3"/>
-        <v>0.7617504051863857</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+        <v>0.75911986103068907</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="4"/>
+        <v>0.21244635193133046</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="5"/>
+        <v>0.79838709677419351</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="13"/>
       <c r="B12" s="9">
         <v>1331</v>
@@ -4044,6 +5379,37 @@
         <f>AVERAGE(O2:O11)</f>
         <v>0.75953538627768769</v>
       </c>
+      <c r="Q12" s="18">
+        <f t="shared" ref="Q12:R12" si="8">AVERAGE(Q2:Q11)</f>
+        <v>0.97278622410752646</v>
+      </c>
+      <c r="R12" s="18">
+        <f t="shared" si="8"/>
+        <v>0.75877243775332948</v>
+      </c>
+      <c r="T12" s="18">
+        <f t="shared" ref="T12:U12" si="9">AVERAGE(T2:T11)</f>
+        <v>0.20678062384350224</v>
+      </c>
+      <c r="U12" s="18">
+        <f t="shared" si="9"/>
+        <v>0.77016129032258063</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="J13" s="20">
+        <f>J12+K12</f>
+        <v>1347.3000000000002</v>
+      </c>
+      <c r="L13" s="20">
+        <f>I12+L12</f>
+        <v>462.6</v>
+      </c>
+      <c r="Q13"/>
+      <c r="R13"/>
+      <c r="S13"/>
+      <c r="T13"/>
+      <c r="U13"/>
     </row>
   </sheetData>
   <pageMargins left="0.78750000000000009" right="0.78750000000000009" top="1.0249999999999997" bottom="1.0249999999999997" header="0.78750000000000009" footer="0.78750000000000009"/>
